--- a/account_employee_setup/positive_imports/jobs_details.xlsx
+++ b/account_employee_setup/positive_imports/jobs_details.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/henrycole/Desktop/account_employee_setup/positive_imports/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/henrycole/Desktop/automation/hr_regression/account_employee_setup/positive_imports/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9F06313-2DF8-EE42-9632-69175EDBF97A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEA1AC0D-110E-8F4C-A15E-F0CDE5CD845A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-33620" yWindow="2880" windowWidth="22600" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="19820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="jobs_template" sheetId="1" r:id="rId1"/>
@@ -101,21 +101,6 @@
     <t>Part-Time</t>
   </si>
   <si>
-    <t>employee@hr_regression.com</t>
-  </si>
-  <si>
-    <t>line@hr_regression.com</t>
-  </si>
-  <si>
-    <t>finance@hr_regression.com</t>
-  </si>
-  <si>
-    <t>contractor@hr_regression.com</t>
-  </si>
-  <si>
-    <t>volunteer@hr_regression.com</t>
-  </si>
-  <si>
     <t>Employee</t>
   </si>
   <si>
@@ -153,6 +138,21 @@
   </si>
   <si>
     <t>31/12/2023</t>
+  </si>
+  <si>
+    <t>employee@hr-regression.com</t>
+  </si>
+  <si>
+    <t>line@hr-regression.com</t>
+  </si>
+  <si>
+    <t>finance@hr-regression.com</t>
+  </si>
+  <si>
+    <t>contractor@hr-regression.com</t>
+  </si>
+  <si>
+    <t>volunteer@hr-regression.com</t>
   </si>
 </sst>
 </file>
@@ -580,19 +580,19 @@
     </row>
     <row r="2" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="C2" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>24</v>
@@ -600,19 +600,19 @@
     </row>
     <row r="3" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>24</v>
@@ -620,19 +620,19 @@
     </row>
     <row r="4" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>24</v>
@@ -640,25 +640,25 @@
     </row>
     <row r="5" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="E5" s="2" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>24</v>
@@ -666,19 +666,19 @@
     </row>
     <row r="6" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="E6" s="2" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>25</v>
@@ -1694,7 +1694,7 @@
           <x14:formula1>
             <xm:f>validations!$A$1:$A$16</xm:f>
           </x14:formula1>
-          <xm:sqref>A2:A1001</xm:sqref>
+          <xm:sqref>A7:A1001</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000001000000}">
           <x14:formula1>
